--- a/excel_routes/route_HMB_DMM_threats.xlsx
+++ b/excel_routes/route_HMB_DMM_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-315</t>
+          <t>Nesma Airlines NE-150</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>11358</v>
+        <v>14283</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17083</v>
+        <v>17255</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-5725</v>
+        <v>-2972</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -591,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12843</v>
+        <v>11579</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17083</v>
+        <v>20242</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4240</v>
+        <v>-8663</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-233</t>
+          <t>Nile Air NP-133</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13080</v>
+        <v>11636</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17083</v>
+        <v>20242</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4003</v>
+        <v>-8606</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -677,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-231</t>
+          <t>Nile Air NP-233</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>13080</v>
+        <v>13221</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17083</v>
+        <v>20242</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4003</v>
+        <v>-7021</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-133</t>
+          <t>flyadeal F3-912</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13080</v>
+        <v>9328</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17083</v>
+        <v>17255</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4003</v>
+        <v>-7927</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -767,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-150</t>
+          <t>flynas XY-855</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>822</v>
+        <v>10631</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14851</v>
+        <v>17255</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-14029</v>
+        <v>-6624</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -812,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>Nesma Airlines NE-150</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>826</v>
+        <v>11579</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14851</v>
+        <v>17255</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-14025</v>
+        <v>-5676</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,393 +866,33 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-697</t>
+          <t>flynas XY-895</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1086</v>
+        <v>10631</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14851</v>
+        <v>13504</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-13765</v>
+        <v>-2873</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-681</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>1086</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>14851</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-13765</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-683</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>1253</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>14851</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-13598</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-687</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>1269</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>14851</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-13582</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-6447</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>1652</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>14851</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-13199</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-912</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>9747</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>14851</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-5104</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-895</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>10473</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>14851</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-4378</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-855</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>11449</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>14851</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-3402</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>07-SEP-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-331</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>10654</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>14851</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-4197</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_DMM_threats.xlsx
+++ b/excel_routes/route_HMB_DMM_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-150</t>
+          <t>Nile Air NP-233</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>14283</v>
+        <v>11636</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17255</v>
+        <v>20242</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2972</v>
+        <v>-8606</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -596,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-154</t>
+          <t>Nile Air NP-133</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11579</v>
+        <v>11636</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>20242</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-8663</v>
+        <v>-8606</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,7 +608,7 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -641,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-133</t>
+          <t>Nile Air NP-231</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11636</v>
+        <v>13221</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>20242</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-8606</v>
+        <v>-7021</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -664,235 +655,10 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-233</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>13221</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>20242</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-7021</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-912</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>9328</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>17255</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-7927</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-855</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>10631</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>17255</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-6624</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-150</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>11579</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>17255</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-5676</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-895</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>10631</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>13504</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-2873</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_DMM_threats.xlsx
+++ b/excel_routes/route_HMB_DMM_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-233</t>
+          <t>Nesma Airlines NE-154</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>11636</v>
+        <v>11570</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20242</v>
+        <v>20236</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-8606</v>
+        <v>-8666</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -587,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-133</t>
+          <t>Nile Air NP-233</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11636</v>
+        <v>11612</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20242</v>
+        <v>20236</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-8606</v>
+        <v>-8624</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -632,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-231</t>
+          <t>Nile Air NP-133</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13221</v>
+        <v>11612</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20242</v>
+        <v>20236</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-7021</v>
+        <v>-8624</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,12 +662,597 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-150</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>10668</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>17249</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-6581</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-895</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>11880</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>17249</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-5369</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-855</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>12866</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>17249</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-4383</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-150</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>10668</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-2832</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>9794</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-3706</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-697</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>11908</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-1592</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-681</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>11908</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-1592</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-912</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>7595</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>14994</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-7399</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-895</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>7595</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>14994</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-7399</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-331</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>8075</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>14994</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-6919</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>7595</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>14994</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-7399</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-697</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>11908</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>14994</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-3086</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-681</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>11908</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>14994</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-3086</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_DMM_threats.xlsx
+++ b/excel_routes/route_HMB_DMM_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,20 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -470,7 +461,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -541,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-154</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>11570</v>
+        <v>9822</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20236</v>
+        <v>13500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-8666</v>
+        <v>-3678</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-233</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11612</v>
+        <v>11908</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20236</v>
+        <v>13500</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-8624</v>
+        <v>-1592</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-133</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11612</v>
+        <v>11908</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20236</v>
+        <v>13500</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-8624</v>
+        <v>-1592</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-150</t>
+          <t>Air Arabia Egypt E5-315</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10668</v>
+        <v>9263</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>17249</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-6581</v>
+        <v>-7986</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -721,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-895</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11880</v>
+        <v>11908</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>17249</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5369</v>
+        <v>-5341</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-855</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12866</v>
+        <v>12500</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>17249</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4383</v>
+        <v>-4749</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-150</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10668</v>
+        <v>10766</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13500</v>
+        <v>15008</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2832</v>
+        <v>-4242</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,7 +833,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,28 +857,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9794</v>
+        <v>11908</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13500</v>
+        <v>15008</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3706</v>
+        <v>-3100</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-697</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11908</v>
+        <v>12500</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13500</v>
+        <v>15008</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1592</v>
+        <v>-2508</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,7 +923,7 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,28 +947,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11908</v>
+        <v>11612</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13500</v>
+        <v>15008</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1592</v>
+        <v>-3396</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7595</v>
+        <v>8441</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14994</v>
+        <v>15008</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-7399</v>
+        <v>-6567</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>15</v>
@@ -1022,7 +1013,7 @@
       <c r="I12" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7595</v>
+        <v>9146</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>14994</v>
+        <v>15008</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-7399</v>
+        <v>-5862</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>15</v>
@@ -1067,7 +1058,7 @@
       <c r="I13" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1082,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>Nile Air NP-231</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8075</v>
+        <v>10766</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14994</v>
+        <v>15008</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-6919</v>
+        <v>-4242</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,9 +1103,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-231</t>
+          <t>flyadeal F3-912</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
         <v>7595</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14994</v>
+        <v>15008</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-7399</v>
+        <v>-7413</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1172,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-697</t>
+          <t>flynas XY-895</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11908</v>
+        <v>7595</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14994</v>
+        <v>15008</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3086</v>
+        <v>-7413</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>14-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1217,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11908</v>
+        <v>8075</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>14994</v>
+        <v>15008</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3086</v>
+        <v>-6933</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">

--- a/excel_routes/route_HMB_DMM_threats.xlsx
+++ b/excel_routes/route_HMB_DMM_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,14 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>Air Arabia Egypt E5-315</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9822</v>
+        <v>10317</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13500</v>
+        <v>20251</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3678</v>
+        <v>-9934</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-697</t>
+          <t>Nesma Airlines NE-154</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11908</v>
+        <v>11570</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13500</v>
+        <v>20251</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1592</v>
+        <v>-8681</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>Nile Air NP-133</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11908</v>
+        <v>11612</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13500</v>
+        <v>20251</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1592</v>
+        <v>-8639</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,28 +686,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-315</t>
+          <t>Nesma Airlines NE-150</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9263</v>
+        <v>10682</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>17249</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-7986</v>
+        <v>-6567</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>flynas XY-895</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11908</v>
+        <v>12866</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>17249</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5341</v>
+        <v>-4383</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-683</t>
+          <t>flynas XY-855</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12500</v>
+        <v>12866</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>17249</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4749</v>
+        <v>-4383</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,28 +821,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>Air Arabia Egypt E5-315</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10766</v>
+        <v>9263</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-4242</v>
+        <v>-5745</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,28 +866,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>Nesma Airlines NE-150</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11908</v>
+        <v>10682</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3100</v>
+        <v>-4326</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,28 +911,28 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-683</t>
+          <t>Nile Air NP-231</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12500</v>
+        <v>10766</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2508</v>
+        <v>-4242</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11612</v>
+        <v>9822</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15008</v>
+        <v>13500</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3396</v>
+        <v>-3678</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -968,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-912</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8441</v>
+        <v>11908</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15008</v>
+        <v>13500</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-6567</v>
+        <v>-1592</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,28 +1046,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-895</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9146</v>
+        <v>11908</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>15008</v>
+        <v>13500</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-5862</v>
+        <v>-1592</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-231</t>
+          <t>Air Arabia Egypt E5-315</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10766</v>
+        <v>9263</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15008</v>
+        <v>17249</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4242</v>
+        <v>-7986</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-912</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7595</v>
+        <v>11908</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15008</v>
+        <v>17249</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-7413</v>
+        <v>-5341</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-895</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7595</v>
+        <v>12500</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>15008</v>
+        <v>17249</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-7413</v>
+        <v>-4749</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1221,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8075</v>
+        <v>10766</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-6933</v>
+        <v>-4242</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1238,12 +1247,597 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>27-JUL-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-681</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>11908</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-3100</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>27-JUL-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-683</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-2508</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-331</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>11612</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-3396</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>07-SEP-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-895</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>12866</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-2142</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-895</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>9146</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-5862</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-912</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>9287</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-5721</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-231</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>10766</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-4242</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-912</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>7595</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-7413</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-895</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>7595</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-7413</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-331</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>8075</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-6933</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-231</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>7595</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-7413</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-697</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>11908</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-3100</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-681</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>11908</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>15008</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-3100</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_DMM_threats.xlsx
+++ b/excel_routes/route_HMB_DMM_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10317</v>
+        <v>10312</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>20251</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-9934</v>
+        <v>-9939</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>20</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9263</v>
+        <v>9258</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-5745</v>
+        <v>-5750</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>20</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9822</v>
+        <v>10710</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13500</v>
+        <v>11781</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3678</v>
+        <v>-1071</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-697</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11908</v>
+        <v>9639</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13500</v>
+        <v>10653</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1592</v>
+        <v>-1014</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>Air Arabia Egypt E5-315</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11908</v>
+        <v>9258</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13500</v>
+        <v>17249</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1592</v>
+        <v>-7991</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-315</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9263</v>
+        <v>11908</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>17249</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-7986</v>
+        <v>-5341</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11908</v>
+        <v>12500</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>17249</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-5341</v>
+        <v>-4749</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-683</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12500</v>
+        <v>10766</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17249</v>
+        <v>15008</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4749</v>
+        <v>-4242</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>10766</v>
+        <v>11908</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4242</v>
+        <v>-3100</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11908</v>
+        <v>12500</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-3100</v>
+        <v>-2508</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>07-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-683</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>12500</v>
+        <v>11612</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2508</v>
+        <v>-3396</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>Nile Air NP-231</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>11612</v>
+        <v>7595</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-3396</v>
+        <v>-7413</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>12866</v>
+        <v>10329</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2142</v>
+        <v>-4679</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>40</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-895</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9146</v>
+        <v>11908</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-5862</v>
+        <v>-3100</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
@@ -1478,366 +1478,6 @@
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-912</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>9287</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-5721</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>11-SEP-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-231</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>10766</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-4242</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>14-SEP-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-912</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>7595</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-7413</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>14-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-895</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>7595</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-7413</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>14-SEP-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-331</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>8075</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-6933</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-231</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>7595</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-7413</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-697</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>11908</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-3100</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-681</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>11908</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-3100</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_DMM_threats.xlsx
+++ b/excel_routes/route_HMB_DMM_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-315</t>
+          <t>Nesma Airlines NE-154</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10312</v>
+        <v>10666</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20251</v>
+        <v>17256</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-9939</v>
+        <v>-6590</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -596,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-154</t>
+          <t>Nile Air NP-233</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11570</v>
+        <v>11602</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20251</v>
+        <v>17256</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-8681</v>
+        <v>-5654</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +608,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -645,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11612</v>
+        <v>11602</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20251</v>
+        <v>17256</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-8639</v>
+        <v>-5654</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -690,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10682</v>
+        <v>9759</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17249</v>
+        <v>13500</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-6567</v>
+        <v>-3741</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +698,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-895</t>
+          <t>Air Arabia Egypt E5-315</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12866</v>
+        <v>8582</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17249</v>
+        <v>13500</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4383</v>
+        <v>-4918</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-855</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12866</v>
+        <v>9773</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>17249</v>
+        <v>13500</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4383</v>
+        <v>-3727</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,28 +812,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-315</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9258</v>
+        <v>12383</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15008</v>
+        <v>13500</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-5750</v>
+        <v>-1117</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,28 +857,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-150</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10682</v>
+        <v>10094</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15008</v>
+        <v>10638</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4326</v>
+        <v>-544</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +902,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-231</t>
+          <t>Air Arabia Egypt E5-315</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10766</v>
+        <v>9183</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15008</v>
+        <v>17256</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4242</v>
+        <v>-8073</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +947,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-697</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10710</v>
+        <v>12383</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11781</v>
+        <v>17256</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1071</v>
+        <v>-4873</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,9 +968,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9639</v>
+        <v>12970</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10653</v>
+        <v>17256</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1014</v>
+        <v>-4286</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,9 +1013,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9258</v>
+        <v>9619</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17249</v>
+        <v>15008</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-7991</v>
+        <v>-5389</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>20</v>
@@ -1067,9 +1058,9 @@
       <c r="I13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,13 +1086,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11908</v>
+        <v>12383</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17249</v>
+        <v>15008</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5341</v>
+        <v>-2625</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1112,9 +1103,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,13 +1131,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12500</v>
+        <v>12970</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17249</v>
+        <v>15008</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4749</v>
+        <v>-2038</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1148,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1172,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>flyadeal F3-912</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10766</v>
+        <v>8362</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4242</v>
+        <v>-6646</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,28 +1217,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>flynas XY-895</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11908</v>
+        <v>9061</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3100</v>
+        <v>-5947</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1261,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,28 +1262,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-683</t>
+          <t>Nile Air NP-231</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12500</v>
+        <v>10736</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2508</v>
+        <v>-4272</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1306,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07-SEP-26</t>
+          <t>18-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,28 +1307,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>flyadeal F3-912</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11612</v>
+        <v>7525</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3396</v>
+        <v>-7483</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1361,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-231</t>
+          <t>flynas XY-895</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7595</v>
+        <v>7525</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-7413</v>
+        <v>-7483</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1406,26 +1397,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-895</t>
+          <t>Nile Air NP-231</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10329</v>
+        <v>7539</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>15008</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4679</v>
+        <v>-7469</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1433,51 +1424,6 @@
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>18-SEP-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-697</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>11908</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-3100</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_DMM_threats.xlsx
+++ b/excel_routes/route_HMB_DMM_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,14 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-154</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10666</v>
+        <v>7976</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17256</v>
+        <v>13386</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-6590</v>
+        <v>-5410</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-233</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11602</v>
+        <v>7976</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17256</v>
+        <v>11675</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5654</v>
+        <v>-3699</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -610,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,28 +641,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-133</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11602</v>
+        <v>9950</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17256</v>
+        <v>13386</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-5654</v>
+        <v>-3436</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -677,28 +686,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-150</t>
+          <t>EgyptAir MS-687</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9759</v>
+        <v>10888</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13500</v>
+        <v>13386</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3741</v>
+        <v>-2498</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-315</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8582</v>
+        <v>9950</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13500</v>
+        <v>11675</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4918</v>
+        <v>-1725</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-331</t>
+          <t>EgyptAir MS-687</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9773</v>
+        <v>10888</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13500</v>
+        <v>11675</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3727</v>
+        <v>-787</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12383</v>
+        <v>9370</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13500</v>
+        <v>10543</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1117</v>
+        <v>-1173</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -833,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-697</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10094</v>
+        <v>9370</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10638</v>
+        <v>10543</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-544</v>
+        <v>-1173</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -878,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-315</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9183</v>
+        <v>8721</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17256</v>
+        <v>11675</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-8073</v>
+        <v>-2954</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-681</t>
+          <t>EgyptAir MS-687</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12383</v>
+        <v>10170</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>17256</v>
+        <v>11675</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4873</v>
+        <v>-1505</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -970,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-683</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12970</v>
+        <v>9370</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17256</v>
+        <v>10543</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4286</v>
+        <v>-1173</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1015,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,28 +1046,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-315</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9619</v>
+        <v>10088</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>15008</v>
+        <v>10543</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-5389</v>
+        <v>-455</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1086,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12383</v>
+        <v>10088</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15008</v>
+        <v>17112</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2625</v>
+        <v>-7024</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1103,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12970</v>
+        <v>10667</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15008</v>
+        <v>17112</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2038</v>
+        <v>-6445</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1148,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-912</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8362</v>
+        <v>11081</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>15008</v>
+        <v>17112</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-6646</v>
+        <v>-6031</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-895</t>
+          <t>EgyptAir MS-697</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9061</v>
+        <v>11081</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15008</v>
+        <v>14876</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-5947</v>
+        <v>-3795</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-231</t>
+          <t>EgyptAir MS-681</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10736</v>
+        <v>11081</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15008</v>
+        <v>14876</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4272</v>
+        <v>-3795</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-912</t>
+          <t>EgyptAir MS-683</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7525</v>
+        <v>11661</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15008</v>
+        <v>14876</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-7483</v>
+        <v>-3215</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1342,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>18-SEP-26</t>
+          <t>11-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-895</t>
+          <t>flyadeal F3-912</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7525</v>
+        <v>8266</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15008</v>
+        <v>14876</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-7483</v>
+        <v>-6610</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>15</v>
@@ -1373,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1387,43 +1396,358 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-895</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>8956</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-5920</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>11-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-231</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>10640</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-4236</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-912</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>7438</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-7438</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-331</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>8997</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-5879</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-895</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>10115</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-4761</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>18-SEP-26</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-437</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-895</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>7438</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-7438</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Nile Air NP-231</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>7539</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>15008</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-7469</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
+      <c r="D27" s="2" t="n">
+        <v>7976</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-6900</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-437</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-697</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>10571</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-4305</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
